--- a/site/exports/nwpu-cs-computer-science-software.xlsx
+++ b/site/exports/nwpu-cs-computer-science-software.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0dc562f5a278436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R4059f4f451e745c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ref22ce6a971d436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R121e3d9a39974df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R5aa1e5e8b5d54802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9be37d6044cb4853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R52a955a60088429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R86e2c357e73847ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R7eede7f3fbf14fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R68050c4c8b3447ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T29_0" displayName="T29_0" ref="A1:K3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T31_0" displayName="T31_0" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T29_1" displayName="T29_1" ref="A1:S7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T31_1" displayName="T31_1" ref="A1:S21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T29_3" displayName="T29_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T31_3" displayName="T31_3" ref="A1:L4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T29_4" displayName="T29_4" ref="A1:G12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T31_4" displayName="T31_4" ref="A1:G24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -528,10 +528,109 @@
         <x:v>西北工业大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>计算机学院·计算机科学与软件系</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str"/>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>本批仅可核公开职业事实，学历缺失不补猜；个人页412停止不绕。；本人明确导师未取得，不从团队成员名单或合著推指导。；张捷团队毕业生栏目不足认定本人博士导师，未建边。</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>学校官方教学报道（非个人主页）：https://news.nwpu.edu.cn/info/1003/120159.htm；复旦大学托管团队职业记录（非本人授位学校证明）：https://faculty.fudan.edu.cn/zhangjie1234/zh_CN/zdylm/849314/list/index.htm</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>计算机学院·计算机科学与软件系</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str"/>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>本批仅可核公开职业事实，学历缺失不补猜；个人页412停止不绕。；本人明确导师未取得，不从团队成员名单或合著推指导。；无直接逐篇出版题录核验，精选书目暂空。</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>学校官方历史职业报道（非个人主页）：https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>计算机学院·计算机科学与软件系</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str"/>
+      <x:c r="E6" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>本批仅可核公开职业事实，学历缺失不补猜；个人页412停止不绕。；本人明确导师未取得，不从团队成员名单或合著推指导。；本科硕士、博士导师未知；访问研究组负责人未作指导关系。</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>学校官方历史职业报道（非个人主页）：https://jsj.nwpu.edu.cn/info/1598/10672.htm；出版者作者职业简介（非学校个人主页）：https://link.springer.com/article/10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45af542a46fc4e7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6738934e13ea49ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -888,10 +987,592 @@
         <x:v>西北工业大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str"/>
+      <x:c r="E8" s="6" t="str"/>
+      <x:c r="F8" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str"/>
+      <x:c r="H8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str"/>
+      <x:c r="K8" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str"/>
+      <x:c r="M8" s="7" t="str"/>
+      <x:c r="N8" s="6" t="str"/>
+      <x:c r="O8" s="6" t="str">
+        <x:v>团队毕业生栏明确博士2018毕业及西工大教授去向；未明确授位机构，不能据页面在复旦就认复旦授位。</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q8" s="6" t="str">
+        <x:v>https://faculty.fudan.edu.cn/zhangjie1234/zh_CN/zdylm/849314/list/index.htm</x:v>
+      </x:c>
+      <x:c r="R8" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S8" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str"/>
+      <x:c r="D9" s="6" t="str">
+        <x:v>哈佛大学医学院</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str"/>
+      <x:c r="F9" s="6" t="str"/>
+      <x:c r="G9" s="6" t="str"/>
+      <x:c r="H9" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L9" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="7" t="str"/>
+      <x:c r="N9" s="6" t="str"/>
+      <x:c r="O9" s="6" t="str">
+        <x:v>同一履历行明确博士后去向；起讫未披露。</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q9" s="6" t="str">
+        <x:v>https://faculty.fudan.edu.cn/zhangjie1234/zh_CN/zdylm/849314/list/index.htm</x:v>
+      </x:c>
+      <x:c r="R9" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S9" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>西北工业大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str"/>
+      <x:c r="F10" s="6" t="str"/>
+      <x:c r="G10" s="6" t="str"/>
+      <x:c r="H10" s="6" t="str"/>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str"/>
+      <x:c r="K10" s="6" t="str"/>
+      <x:c r="L10" s="6" t="str"/>
+      <x:c r="M10" s="7" t="str"/>
+      <x:c r="N10" s="6" t="str"/>
+      <x:c r="O10" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="str"/>
+      <x:c r="Q10" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
+      </x:c>
+      <x:c r="R10" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S10" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>授课教师</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>西北工业大学哈萨克斯坦分校</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str"/>
+      <x:c r="F11" s="6" t="str"/>
+      <x:c r="G11" s="6" t="str"/>
+      <x:c r="H11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str"/>
+      <x:c r="K11" s="6" t="str"/>
+      <x:c r="L11" s="6" t="str"/>
+      <x:c r="M11" s="7" t="str"/>
+      <x:c r="N11" s="6" t="str"/>
+      <x:c r="O11" s="6" t="str">
+        <x:v>2024.05.29新闻明确参与Data Mining Techniques授课，不把团队2.11起派出当个人起始，也非学历或长期校区归属。</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="str"/>
+      <x:c r="Q11" s="6" t="str">
+        <x:v>https://news.nwpu.edu.cn/info/1003/120159.htm</x:v>
+      </x:c>
+      <x:c r="R11" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S11" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str"/>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L12" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="7" t="str"/>
+      <x:c r="N12" s="6" t="str"/>
+      <x:c r="O12" s="6" t="str">
+        <x:v>人力资源部2022.12.08正文明确2016获博士但未给学校，不借第三方填哈尔滨工业大学。</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q12" s="6" t="str">
+        <x:v>https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="R12" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S12" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str"/>
+      <x:c r="D13" s="6" t="str">
+        <x:v>哈佛大学</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str"/>
+      <x:c r="F13" s="6" t="str"/>
+      <x:c r="G13" s="6" t="str"/>
+      <x:c r="H13" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L13" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="7" t="str"/>
+      <x:c r="N13" s="6" t="str"/>
+      <x:c r="O13" s="6" t="str">
+        <x:v>校方明确曾赴哈佛博士后，日期未知。</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q13" s="6" t="str">
+        <x:v>https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="R13" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S13" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>西北工业大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str"/>
+      <x:c r="F14" s="6" t="str"/>
+      <x:c r="G14" s="6" t="str"/>
+      <x:c r="H14" s="6" t="str"/>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str"/>
+      <x:c r="K14" s="6" t="str"/>
+      <x:c r="L14" s="6" t="str"/>
+      <x:c r="M14" s="7" t="str"/>
+      <x:c r="N14" s="6" t="str"/>
+      <x:c r="O14" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P14" s="6" t="str"/>
+      <x:c r="Q14" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
+      </x:c>
+      <x:c r="R14" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S14" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>入职</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str"/>
+      <x:c r="G15" s="6" t="str"/>
+      <x:c r="H15" s="6" t="str"/>
+      <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str"/>
+      <x:c r="K15" s="6" t="str"/>
+      <x:c r="L15" s="6" t="str"/>
+      <x:c r="M15" s="7" t="str"/>
+      <x:c r="N15" s="6" t="str"/>
+      <x:c r="O15" s="6" t="str">
+        <x:v>原文入职年份不当教授晋升年。</x:v>
+      </x:c>
+      <x:c r="P15" s="6" t="str"/>
+      <x:c r="Q15" s="6" t="str">
+        <x:v>https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="R15" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S15" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>长聘副教授</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>西北工业大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str"/>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str"/>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str"/>
+      <x:c r="L16" s="6" t="str"/>
+      <x:c r="M16" s="7" t="str"/>
+      <x:c r="N16" s="6" t="str"/>
+      <x:c r="O16" s="6" t="str">
+        <x:v>2022年新闻历史职称；当前名录教授，晋升时间未知。</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="str"/>
+      <x:c r="Q16" s="6" t="str">
+        <x:v>https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="R16" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S16" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>马格德堡大学</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str"/>
+      <x:c r="F17" s="6" t="str">
+        <x:v>2005-10</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>计算机科学</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>德国</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str">
+        <x:v>德国</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L17" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="str"/>
+      <x:c r="N17" s="6" t="str"/>
+      <x:c r="O17" s="6" t="str">
+        <x:v>出版者作者简介明确2005.10获得；校方新闻独立确认2005德国获博士。</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q17" s="6" t="str">
+        <x:v>https://link.springer.com/article/10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S17" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>academic_visit</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str"/>
+      <x:c r="D18" s="6" t="str">
+        <x:v>伦斯勒理工学院</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str"/>
+      <x:c r="H18" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L18" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="str"/>
+      <x:c r="N18" s="6" t="str"/>
+      <x:c r="O18" s="6" t="str">
+        <x:v>在Zaki Mohammed领导研究组访学，不等同直接明确导师。</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q18" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/info/1598/10672.htm</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>西北工业大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str"/>
+      <x:c r="L19" s="6" t="str"/>
+      <x:c r="M19" s="7" t="str"/>
+      <x:c r="N19" s="6" t="str"/>
+      <x:c r="O19" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="str"/>
+      <x:c r="Q19" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S19" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>引进人才入职</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="str">
+        <x:v>2005-11</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str"/>
+      <x:c r="L20" s="6" t="str"/>
+      <x:c r="M20" s="7" t="str"/>
+      <x:c r="N20" s="6" t="str"/>
+      <x:c r="O20" s="6" t="str"/>
+      <x:c r="P20" s="6" t="str"/>
+      <x:c r="Q20" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/info/1598/10672.htm</x:v>
+      </x:c>
+      <x:c r="R20" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>副院长</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>西北工业大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str"/>
+      <x:c r="L21" s="6" t="str"/>
+      <x:c r="M21" s="7" t="str"/>
+      <x:c r="N21" s="6" t="str"/>
+      <x:c r="O21" s="6" t="str">
+        <x:v>2022新闻所述历史任职，不当现职。</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="str"/>
+      <x:c r="Q21" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/info/1598/10672.htm</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="S21" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4aff30c4fce4fe6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0272397dc0c4775"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1089,10 +1770,48 @@
         <x:v>西北工业大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>DeMa: dual-path delay-aware Mamba for efficient multivariate time series analysis</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>https://link.springer.com/article/10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>https://link.springer.com/article/10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://teacher.nwpu.edu.cn/Shang.html</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>出版社文章元数据已核，不表示全文已读。；article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>出版者明确Xuequn Shang西工大计算机单位和作者简介，20:2011630。</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce537c07c0574c98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d63b1ef387f4906"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1342,16 +2061,16 @@
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
-        <x:v>陈群</x:v>
+        <x:v>刘曌雯</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>liuzhaowen-source-1</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
       </x:c>
       <x:c r="E11" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1365,31 +2084,307 @@
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>liuzhaowen-source-2</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>https://teacher.nwpu.edu.cn/zhaowenliu</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>个人门户返回412后停止，未绕过或重试。；http_412_stopped</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>liuzhaowen-source-3</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>https://faculty.fudan.edu.cn/zhangjie1234/zh_CN/zdylm/849314/list/index.htm</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>刘曌雯</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>liuzhaowen-source-4</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>https://news.nwpu.edu.cn/info/1003/120159.htm</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>pengjiajie-source-1</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>pengjiajie-source-2</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>https://teacher.nwpu.edu.cn/peng.html</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>个人门户返回412后停止，未绕过或重试。；http_412_stopped</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>pengjiajie-source-3</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>https://renshi.nwpu.edu.cn/info/1437/15955.htm</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>shangxuequn-source-1</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/snew/szdwlist.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1519</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>shangxuequn-source-2</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>https://teacher.nwpu.edu.cn/Shang.html</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>个人门户返回412后停止，未绕过或重试。；http_412_stopped</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>shangxuequn-source-3</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>https://jsj.nwpu.edu.cn/info/1598/10672.htm</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>尚学群</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>shangxuequn-source-4</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>https://link.springer.com/article/10.1007/s11704-026-52221-6</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>出版者文章元数据及作者职业简介已读，非学校主页。；publisher_metadata_and_biography_read</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
         <x:v>陈群</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="B22" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>陈群</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
         <x:v>institution-classification-6</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C23" s="6" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D23" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F12" s="6" t="str">
-        <x:v>nwpu</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str">
+      <x:c r="E23" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>西北工业大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>彭佳杰</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>nwpu</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
         <x:v>西北工业大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e85172e03644a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4726fe0d07e41af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/nwpu-cs-computer-science-software.xlsx
+++ b/site/exports/nwpu-cs-computer-science-software.xlsx
@@ -452,7 +452,7 @@
     <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
     <col width="44.8" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
